--- a/employeeslip.xlsx
+++ b/employeeslip.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thevaasiinenchandereng/Desktop/HRapp/Payroll-dev/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{033CEBF3-BA6C-0447-BE07-73E9657C635F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0328DB75-687C-1847-BE08-67421AA33A86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="560" yWindow="1000" windowWidth="25040" windowHeight="13900" xr2:uid="{C8E678A0-6F07-1043-81A4-86E8881D5276}"/>
+    <workbookView xWindow="560" yWindow="980" windowWidth="25040" windowHeight="13900" xr2:uid="{C8E678A0-6F07-1043-81A4-86E8881D5276}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
   <si>
     <t>HIGH ACUMEN SDN BHD(888365-X)</t>
   </si>
@@ -77,9 +77,6 @@
     <t>ADVANCE</t>
   </si>
   <si>
-    <t>ATTENDANCE ALLOWANCES</t>
-  </si>
-  <si>
     <t>ALLOWANCE PREPAYMENT</t>
   </si>
   <si>
@@ -120,6 +117,15 @@
   </si>
   <si>
     <t xml:space="preserve">I/C NO: </t>
+  </si>
+  <si>
+    <t>OVERTIME</t>
+  </si>
+  <si>
+    <t>ATTENDANCE ALLOWANCE</t>
+  </si>
+  <si>
+    <t>OTHER</t>
   </si>
 </sst>
 </file>
@@ -181,7 +187,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -405,17 +411,6 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top/>
       <bottom/>
       <diagonal/>
@@ -431,28 +426,6 @@
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -532,7 +505,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -558,15 +531,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -604,40 +568,31 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -655,19 +610,19 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1032,7 +987,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE9D5786-7DEB-5645-81A1-37D1F28BE517}">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.5" customWidth="1"/>
@@ -1042,24 +997,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="29" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="49"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="43"/>
     </row>
     <row r="2" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="52"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="46"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -1069,7 +1024,7 @@
     </row>
     <row r="4" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="7" t="s">
@@ -1078,166 +1033,158 @@
       <c r="D4" s="8"/>
     </row>
     <row r="5" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="11"/>
-    </row>
-    <row r="6" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>5</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B6" s="13"/>
       <c r="C6" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>5</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="D6" s="15"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="18"/>
+      <c r="A7" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="17"/>
+      <c r="C7" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="19"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="16" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="20"/>
-      <c r="C8" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="22"/>
+      <c r="C8" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="19"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="23"/>
+      <c r="B9" s="20"/>
       <c r="C9" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="22"/>
+        <v>13</v>
+      </c>
+      <c r="D9" s="19"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="23"/>
-      <c r="C10" s="24" t="s">
+      <c r="A10" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="22"/>
+      <c r="C10" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="22"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="25"/>
-      <c r="B11" s="26"/>
-      <c r="C11" s="21" t="s">
+      <c r="D10" s="19"/>
+    </row>
+    <row r="11" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="22"/>
+      <c r="C11" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="22"/>
+      <c r="D11" s="19"/>
     </row>
     <row r="12" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="27"/>
-      <c r="B12" s="26"/>
-      <c r="C12" s="21" t="s">
+      <c r="A12" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="22"/>
+      <c r="B12" s="24">
+        <f>B6+B7+B8+B9+B10</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="26">
+        <f>D6+D7+D8+D10+D11+D9</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="28">
-        <f>B7+B8+B9+B10+B11</f>
-        <v>0</v>
-      </c>
-      <c r="C13" s="29" t="s">
+      <c r="A13" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="30">
-        <f>D7+D8+D9+D11+D12+D10</f>
-        <v>0</v>
-      </c>
+      <c r="B13" s="48"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="49"/>
     </row>
     <row r="14" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="31"/>
-      <c r="B14" s="32"/>
-      <c r="C14" s="32"/>
-      <c r="D14" s="33"/>
-    </row>
-    <row r="15" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="53" t="s">
+      <c r="A14" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="54"/>
-      <c r="C15" s="54"/>
-      <c r="D15" s="55"/>
-    </row>
-    <row r="16" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="31"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="27"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="35" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="35"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="27"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="23" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="37"/>
-      <c r="B17" s="38"/>
-      <c r="C17" s="39"/>
-      <c r="D17" s="33"/>
+      <c r="B17" s="37"/>
+      <c r="C17" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="27"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="40" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="41"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="33"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="43"/>
-      <c r="C19" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" s="33"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="27"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="43"/>
-      <c r="D20" s="45"/>
-    </row>
-    <row r="21" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="5"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="46"/>
+      <c r="A18" s="23"/>
+      <c r="B18" s="37"/>
+      <c r="C18" s="37"/>
+      <c r="D18" s="39"/>
+    </row>
+    <row r="19" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="5"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
